--- a/data/trans_orig/IP07A12-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07A12-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos en 2007 (tasa de respuesta: 99,5%)</t>
+          <t>Menores según la frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos/as, percibida por el adulto en 2007 (tasa de respuesta: 99,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7781</t>
+          <t>7867</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18134</t>
+          <t>18896</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12830</t>
+          <t>13214</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24862</t>
+          <t>25511</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24102</t>
+          <t>24391</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39910</t>
+          <t>40766</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>28,15%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28391</t>
+          <t>28489</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41479</t>
+          <t>41021</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35432</t>
+          <t>35245</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50025</t>
+          <t>49778</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>68801</t>
+          <t>68569</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>87681</t>
+          <t>87319</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,29%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10314</t>
+          <t>9778</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21390</t>
+          <t>20540</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12791</t>
+          <t>12360</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25545</t>
+          <t>24625</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>25824</t>
+          <t>25041</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>42344</t>
+          <t>41263</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>28,49%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4148</t>
+          <t>4345</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3223</t>
+          <t>3436</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>570</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4654</t>
+          <t>5025</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2523</t>
+          <t>2801</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2786</t>
+          <t>3042</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22900</t>
+          <t>22552</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36711</t>
+          <t>36889</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20669</t>
+          <t>21288</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35576</t>
+          <t>34952</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47860</t>
+          <t>48213</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67911</t>
+          <t>67943</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,54%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37875</t>
+          <t>39011</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53203</t>
+          <t>55005</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30551</t>
+          <t>30959</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45744</t>
+          <t>46171</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>72939</t>
+          <t>73060</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>94228</t>
+          <t>94557</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,67%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16454</t>
+          <t>15962</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29357</t>
+          <t>29517</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20361</t>
+          <t>20126</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>34299</t>
+          <t>34914</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>40466</t>
+          <t>39995</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>59205</t>
+          <t>58711</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>28,98%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>660</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6501</t>
+          <t>5982</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>672</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5920</t>
+          <t>6021</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2540</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9836</t>
+          <t>9736</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>662</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5923</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8774</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3334</t>
+          <t>3332</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12029</t>
+          <t>11353</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16459</t>
+          <t>16610</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27468</t>
+          <t>27588</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19757</t>
+          <t>20100</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32918</t>
+          <t>32232</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40226</t>
+          <t>39188</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57246</t>
+          <t>55674</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>43,72%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11717</t>
+          <t>11580</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>22401</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15567</t>
+          <t>15647</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27552</t>
+          <t>27947</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29872</t>
+          <t>30490</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45982</t>
+          <t>47316</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>37,15%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12477</t>
+          <t>12196</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23151</t>
+          <t>23080</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12044</t>
+          <t>11286</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22979</t>
+          <t>22210</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>26521</t>
+          <t>27000</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>41968</t>
+          <t>42472</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>33,35%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1856</t>
+          <t>1858</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8221</t>
+          <t>7920</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>643</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5562</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3009</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10866</t>
+          <t>10983</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3784</t>
+          <t>3611</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3252</t>
+          <t>3221</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4477</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19480</t>
+          <t>19129</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33625</t>
+          <t>34314</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24359</t>
+          <t>23833</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40059</t>
+          <t>39297</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>47248</t>
+          <t>47823</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>68296</t>
+          <t>69274</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>36,24%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>27034</t>
+          <t>27125</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>42707</t>
+          <t>42926</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>35523</t>
+          <t>35374</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>51502</t>
+          <t>51150</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>67266</t>
+          <t>67068</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>90295</t>
+          <t>88615</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>46,35%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>17332</t>
+          <t>17916</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>32263</t>
+          <t>32710</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12274</t>
+          <t>12101</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25269</t>
+          <t>24751</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>34106</t>
+          <t>34348</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>53081</t>
+          <t>53604</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>28,04%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1484</t>
+          <t>1474</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8430</t>
+          <t>8368</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7253</t>
+          <t>7061</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3579</t>
+          <t>3725</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12469</t>
+          <t>12542</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>692</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>6417</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>817</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6829</t>
+          <t>6939</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10043</t>
+          <t>9896</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>78698</t>
+          <t>78941</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>105359</t>
+          <t>103820</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>89171</t>
+          <t>90751</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>116899</t>
+          <t>117555</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>174352</t>
+          <t>175950</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>212231</t>
+          <t>213962</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>32,13%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>115935</t>
+          <t>118648</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>145714</t>
+          <t>146218</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>129971</t>
+          <t>130097</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>159913</t>
+          <t>160744</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>259068</t>
+          <t>256655</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>299854</t>
+          <t>297735</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>44,71%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>67925</t>
+          <t>68341</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>92720</t>
+          <t>91515</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>67209</t>
+          <t>67006</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>91418</t>
+          <t>92220</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>140631</t>
+          <t>142519</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>175830</t>
+          <t>176008</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>7410</t>
+          <t>7708</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>18447</t>
+          <t>18754</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5155</t>
+          <t>4678</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>14644</t>
+          <t>14016</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>14250</t>
+          <t>14257</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>28996</t>
+          <t>28761</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2723</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>10868</t>
+          <t>9901</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4455</t>
+          <t>4547</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>13470</t>
+          <t>14226</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>8480</t>
+          <t>8709</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>20087</t>
+          <t>20910</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos en 2012 (tasa de respuesta: 98,02%)</t>
+          <t>Menores según la frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos/as, percibida por el adulto en 2012 (tasa de respuesta: 98,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21446</t>
+          <t>21075</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35183</t>
+          <t>34920</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24596</t>
+          <t>24791</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39881</t>
+          <t>39120</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49146</t>
+          <t>51001</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69080</t>
+          <t>69948</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>50,58%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19810</t>
+          <t>20114</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33089</t>
+          <t>33587</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16210</t>
+          <t>16892</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30334</t>
+          <t>30394</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41397</t>
+          <t>41452</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>60214</t>
+          <t>60726</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>43,91%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6725</t>
+          <t>6871</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16825</t>
+          <t>16550</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6295</t>
+          <t>6537</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17030</t>
+          <t>17011</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15267</t>
+          <t>15578</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>28995</t>
+          <t>29598</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,4%</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3547</t>
+          <t>2948</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1593</t>
+          <t>1597</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9282</t>
+          <t>9043</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>2124</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9945</t>
+          <t>9582</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>634</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>5475</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>626</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5365</t>
+          <t>5247</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32967</t>
+          <t>33822</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49510</t>
+          <t>49815</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29058</t>
+          <t>29157</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44755</t>
+          <t>44599</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66819</t>
+          <t>66674</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89393</t>
+          <t>88609</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>45,13%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30644</t>
+          <t>30413</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46069</t>
+          <t>46071</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,7 +5184,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32053</t>
+          <t>32539</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47317</t>
+          <t>48222</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>66436</t>
+          <t>66897</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>89551</t>
+          <t>88663</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,15%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10415</t>
+          <t>10730</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22646</t>
+          <t>23424</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10925</t>
+          <t>10975</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23032</t>
+          <t>22489</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>25710</t>
+          <t>24967</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>41732</t>
+          <t>42076</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,43%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>665</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5942</t>
+          <t>6577</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7026</t>
+          <t>6538</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2627</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10812</t>
+          <t>10469</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4652</t>
+          <t>4671</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4338</t>
+          <t>3968</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>609</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6440</t>
+          <t>5847</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20351</t>
+          <t>20336</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33129</t>
+          <t>34044</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26535</t>
+          <t>25618</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38712</t>
+          <t>39141</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>49913</t>
+          <t>51057</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>67437</t>
+          <t>69986</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>51,67%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17796</t>
+          <t>17285</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29939</t>
+          <t>29393</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11610</t>
+          <t>11615</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22064</t>
+          <t>23019</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>32490</t>
+          <t>31021</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48665</t>
+          <t>47671</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,19%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8736</t>
+          <t>9139</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19692</t>
+          <t>19603</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9863</t>
+          <t>9672</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>20366</t>
+          <t>19821</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>20957</t>
+          <t>21584</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>36699</t>
+          <t>36430</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,89%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>651</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5395</t>
+          <t>5504</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7016</t>
+          <t>7417</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2302</t>
+          <t>2186</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9731</t>
+          <t>10106</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6195,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>2741</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>621</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6993</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7021</t>
+          <t>7304</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30341</t>
+          <t>29823</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>46446</t>
+          <t>45869</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26537</t>
+          <t>25965</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41893</t>
+          <t>41212</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>61056</t>
+          <t>59732</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>82807</t>
+          <t>82665</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>44,97%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>19101</t>
+          <t>19534</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>34993</t>
+          <t>34805</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>22931</t>
+          <t>22751</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>37433</t>
+          <t>38429</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>44993</t>
+          <t>46136</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>67362</t>
+          <t>68082</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>37,04%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13883</t>
+          <t>14397</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28250</t>
+          <t>28047</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13465</t>
+          <t>13025</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>26610</t>
+          <t>26569</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>30083</t>
+          <t>30321</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>50439</t>
+          <t>49988</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,2%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1797</t>
+          <t>1666</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>9754</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2770</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11305</t>
+          <t>12280</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6128</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18164</t>
+          <t>18389</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5254</t>
+          <t>5577</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9393</t>
+          <t>8094</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1762</t>
+          <t>2069</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10852</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>117966</t>
+          <t>117786</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>147421</t>
+          <t>148566</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>120179</t>
+          <t>118325</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>148416</t>
+          <t>148672</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>243996</t>
+          <t>247239</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>288369</t>
+          <t>289003</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,2%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>100243</t>
+          <t>100312</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>128659</t>
+          <t>128688</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>98118</t>
+          <t>95873</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>124521</t>
+          <t>126267</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>204397</t>
+          <t>203819</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>244001</t>
+          <t>244778</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,43%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>49612</t>
+          <t>50081</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>73517</t>
+          <t>73224</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>49631</t>
+          <t>49844</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>72883</t>
+          <t>72845</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>106404</t>
+          <t>106535</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>139201</t>
+          <t>139621</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>5671</t>
+          <t>5701</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>16094</t>
+          <t>16593</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>11400</t>
+          <t>11553</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>24443</t>
+          <t>25295</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>19497</t>
+          <t>20386</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>36231</t>
+          <t>38287</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1425</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>8123</t>
+          <t>8718</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>5035</t>
+          <t>5242</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>15158</t>
+          <t>16521</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>8158</t>
+          <t>8242</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>20022</t>
+          <t>19818</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos en 2016 (tasa de respuesta: 98,72%)</t>
+          <t>Menores según la frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos/as, percibida por el adulto en 2016 (tasa de respuesta: 98,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16179</t>
+          <t>15331</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28526</t>
+          <t>28865</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20291</t>
+          <t>19766</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34248</t>
+          <t>34023</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38485</t>
+          <t>39655</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58659</t>
+          <t>59148</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,94%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15158</t>
+          <t>15289</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28959</t>
+          <t>28989</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>15119</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27337</t>
+          <t>28091</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33206</t>
+          <t>33261</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51705</t>
+          <t>52446</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>36,3%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12784</t>
+          <t>13087</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25392</t>
+          <t>25592</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13744</t>
+          <t>13424</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27006</t>
+          <t>26732</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>30794</t>
+          <t>29394</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>48893</t>
+          <t>48807</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,78%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2690</t>
+          <t>2523</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12147</t>
+          <t>12038</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1716</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11092</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6516</t>
+          <t>6539</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18393</t>
+          <t>17880</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,38%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>683</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6854</t>
+          <t>6029</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6006</t>
+          <t>5387</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1469</t>
+          <t>1466</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8284</t>
+          <t>8220</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16828</t>
+          <t>16718</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30493</t>
+          <t>31033</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33627</t>
+          <t>32138</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49413</t>
+          <t>49080</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54036</t>
+          <t>53847</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75555</t>
+          <t>75613</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,38%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30386</t>
+          <t>29342</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45990</t>
+          <t>45603</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28875</t>
+          <t>29071</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44573</t>
+          <t>45887</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>64447</t>
+          <t>63583</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>86500</t>
+          <t>85642</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,07%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28803</t>
+          <t>28575</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44539</t>
+          <t>44614</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15740</t>
+          <t>15046</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>29703</t>
+          <t>29150</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>47449</t>
+          <t>48937</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>68739</t>
+          <t>69241</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,4%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2913</t>
+          <t>2547</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10225</t>
+          <t>10630</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3509</t>
+          <t>3783</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13008</t>
+          <t>12683</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19529</t>
+          <t>19827</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7184</t>
+          <t>7531</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9190,7 +9190,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>1849</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9289</t>
+          <t>8867</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22626</t>
+          <t>22229</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35761</t>
+          <t>35229</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22601</t>
+          <t>22507</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37310</t>
+          <t>36541</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>49077</t>
+          <t>48876</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>68385</t>
+          <t>68198</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>45,91%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12621</t>
+          <t>12770</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24115</t>
+          <t>23977</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11606</t>
+          <t>11762</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24127</t>
+          <t>23817</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27257</t>
+          <t>26986</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43891</t>
+          <t>43790</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,48%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10505</t>
+          <t>10170</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21215</t>
+          <t>21389</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17957</t>
+          <t>18001</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31434</t>
+          <t>31800</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>32481</t>
+          <t>31191</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>51660</t>
+          <t>49014</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>33,0%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2574</t>
+          <t>2349</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10147</t>
+          <t>9787</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9829</t>
+          <t>10165</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>5581</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16365</t>
+          <t>16567</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1142</t>
+          <t>1485</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6777</t>
+          <t>7170</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9872,7 +9872,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4149</t>
+          <t>3736</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2160</t>
+          <t>2146</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8535</t>
+          <t>8352</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23311</t>
+          <t>23431</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40019</t>
+          <t>40058</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23546</t>
+          <t>23862</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39847</t>
+          <t>40290</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>52180</t>
+          <t>52399</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>75931</t>
+          <t>74718</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>35,63%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>27743</t>
+          <t>27814</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>44873</t>
+          <t>44844</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>28273</t>
+          <t>27487</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>43453</t>
+          <t>45195</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>60630</t>
+          <t>59626</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>83657</t>
+          <t>83110</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>39,63%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16167</t>
+          <t>16005</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>31355</t>
+          <t>31347</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,7 +10303,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>22044</t>
+          <t>21474</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>37390</t>
+          <t>36569</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>43110</t>
+          <t>42452</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>63407</t>
+          <t>64214</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,62%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7439</t>
+          <t>7023</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18251</t>
+          <t>19217</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>2157</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9648</t>
+          <t>9753</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11021</t>
+          <t>11357</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23984</t>
+          <t>24385</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>1604</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9689</t>
+          <t>9047</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10554,7 +10554,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2949</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10569,7 +10569,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2214</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10231</t>
+          <t>10725</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>91048</t>
+          <t>90749</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>120282</t>
+          <t>119868</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>113995</t>
+          <t>114917</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>144474</t>
+          <t>143358</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>214699</t>
+          <t>213002</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>255990</t>
+          <t>256550</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,81%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>99833</t>
+          <t>99531</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>128096</t>
+          <t>129450</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>96433</t>
+          <t>96850</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>125192</t>
+          <t>125083</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>203631</t>
+          <t>202881</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>243925</t>
+          <t>244189</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,08%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>80941</t>
+          <t>80969</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>108204</t>
+          <t>109704</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10990,7 +10990,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>80798</t>
+          <t>82938</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>109480</t>
+          <t>112121</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>169896</t>
+          <t>170777</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>209574</t>
+          <t>209320</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,22%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>21397</t>
+          <t>21519</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>38918</t>
+          <t>39387</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>14837</t>
+          <t>14473</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>30543</t>
+          <t>29855</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>40249</t>
+          <t>40644</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>63935</t>
+          <t>65543</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>8659</t>
+          <t>7990</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>20338</t>
+          <t>20383</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1424</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>8825</t>
+          <t>8067</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>11974</t>
+          <t>12069</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>25886</t>
+          <t>26060</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
